--- a/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260907-AGENT-B057/SEO_QA_B057.xlsx
+++ b/resutls/chillgen.com/chillgen_20260907_01/qa/QA-20260907-AGENT-B057/SEO_QA_B057.xlsx
@@ -14,11 +14,11 @@
     <sheet name="QA_Issues" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QA_Summary'!$A$1:$C$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QA_Products'!$A$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QA_Summary'!$A$1:$C$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'QA_Products'!$A$1:$T$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QA_Criteria'!$A$1:$J$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'QA_Images'!$A$1:$X$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA_Issues'!$A$1:$K$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'QA_Issues'!$A$1:$K$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -618,61 +618,61 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Image_Audit rows visually checked via local B057 contact sheets and cross-checked with live gallery counts.</t>
+          <t>Image_Audit rows evaluated with evidence-driven rules over observation and alt fields; direct human visual confirmation remains a limitation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>batch_status</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>QA_PASS</t>
-        </is>
+          <t>image_rows_in_scope</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>All products QA_PASS; QA_PASS is not APPROVED.</t>
+          <t>Image_Audit rows included in this batch scope.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>batch_average_final_score</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>95</v>
+          <t>batch_status</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>QA_REVISE</t>
+        </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Equal average of product final scores.</t>
+          <t>Evidence-driven rerun status; QA_PASS requires complete assessed weight, score &gt;=85, and no CRITICAL/MAJOR.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>qa_pass_count</t>
+          <t>batch_average_final_score</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>9</v>
+        <v>74.38890000000001</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Products meeting &gt;=85 with no CRITICAL/MAJOR.</t>
+          <t>Blank when any product has incomplete assessed weight.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>critical_count</t>
+          <t>qa_pass_count</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -680,14 +680,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>No critical issue found.</t>
+          <t>Products meeting &gt;=85 with no CRITICAL/MAJOR.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>major_count</t>
+          <t>critical_count</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -695,61 +695,93 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Auto MAJOR identity/non-slip findings were downgraded/resolved after live and image QA; remaining deployment constraints are limitations.</t>
+          <t>Products with at least one CRITICAL issue.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>limitation_count</t>
+          <t>major_count</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state and direct demand evidence limitations; do not block content QA but must be acknowledged before approval/deploy.</t>
+          <t>Total MAJOR issues from evidence-driven field/image checks.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>generated_at</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
-        </is>
+          <t>limitation_count</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UTC timestamp.</t>
+          <t>Admin/export before-state, direct demand evidence, and visual-confirmation limitations.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>methodology_status</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>EVIDENCE_DRIVEN_RERUN_NO_FIXED_SCORE</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>No fixed FULL/100/95 scoring is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>UTC timestamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>scope_note</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>QA covers B057 only; no workbook source edit, no approval, no Shopify deploy.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Operational boundary.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C18"/>
+  <autoFilter ref="A1:C20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -760,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -780,8 +812,9 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="46" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -872,10 +905,15 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>limitation_count</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>issue_refs</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>evidence_refs</t>
         </is>
@@ -898,23 +936,23 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -940,17 +978,20 @@
         <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0001;LIM-0002</t>
-        </is>
+      <c r="R2" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>B057-561; live HTTP=200; local contact sheet</t>
         </is>
@@ -973,23 +1014,23 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1015,17 +1056,20 @@
         <v>0</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0003;LIM-0004</t>
-        </is>
+      <c r="R3" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0005;LIM-0006;LIM-0007;AUTO-0008</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>B057-562; live HTTP=200; local contact sheet</t>
         </is>
@@ -1048,23 +1092,23 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1090,17 +1134,20 @@
         <v>0</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0005;LIM-0006</t>
-        </is>
+      <c r="R4" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0009;LIM-0010;LIM-0011;AUTO-0012</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>B057-563; live HTTP=200; local contact sheet</t>
         </is>
@@ -1123,23 +1170,23 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1165,17 +1212,20 @@
         <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0007;LIM-0008</t>
-        </is>
+      <c r="R5" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>B057-564; live HTTP=200; local contact sheet</t>
         </is>
@@ -1198,23 +1248,23 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1240,17 +1290,20 @@
         <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0009;LIM-0010</t>
-        </is>
+      <c r="R6" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0017;LIM-0018;LIM-0019;AUTO-0020</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>B057-565; live HTTP=200; local contact sheet</t>
         </is>
@@ -1273,23 +1326,23 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>95</v>
+        <v>70.5</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1315,17 +1368,20 @@
         <v>0</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0011;LIM-0012</t>
-        </is>
+      <c r="R7" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0021;LIM-0022;LIM-0023;AUTO-0024</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>B057-566; live HTTP=200; local contact sheet</t>
         </is>
@@ -1348,23 +1404,23 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1390,17 +1446,20 @@
         <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0013;LIM-0014</t>
-        </is>
+      <c r="R8" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0025;LIM-0026;LIM-0027;AUTO-0028</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>B057-567; live HTTP=200; local contact sheet</t>
         </is>
@@ -1423,23 +1482,23 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1465,17 +1524,20 @@
         <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0015;LIM-0016</t>
-        </is>
+      <c r="R9" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>B057-568; live HTTP=200; local contact sheet</t>
         </is>
@@ -1498,23 +1560,23 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>QA_PASS</t>
+          <t>QA_REVISE</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1540,24 +1602,27 @@
         <v>0</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>LIM-0017;LIM-0018</t>
-        </is>
+      <c r="R10" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
+          <t>LIM-0033;LIM-0034;LIM-0035;AUTO-0036</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
           <t>B057-569; live HTTP=200; local contact sheet</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S10"/>
+  <autoFilter ref="A1:T10"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -1591,7 +1656,7 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1676,7 +1741,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1702,21 +1767,21 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -1756,7 +1821,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1796,7 +1861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1822,21 +1887,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1846,7 +1911,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>LIM-0001;LIM-0002</t>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1945,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 42; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1920,7 +1985,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 42; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1960,7 +2025,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 133; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2000,7 +2065,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 74 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2018,29 +2083,29 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2048,7 +2113,11 @@
           <t>B057-561; live=https://chillgen.com/products/custom-golf-area-rug-d8623da216</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2058,29 +2127,29 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2090,7 +2159,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>LIM-0001;LIM-0002</t>
+          <t>LIM-0001;LIM-0002;LIM-0003;AUTO-0004</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2193,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2150,21 +2219,21 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2204,7 +2273,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2244,7 +2313,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2270,21 +2339,21 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2294,7 +2363,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>LIM-0003;LIM-0004</t>
+          <t>LIM-0005;LIM-0006;LIM-0007;AUTO-0008</t>
         </is>
       </c>
     </row>
@@ -2314,21 +2383,21 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 30, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2354,21 +2423,21 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 30, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2394,21 +2463,21 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 114; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2448,7 +2517,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 69 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2466,29 +2535,29 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2496,7 +2565,11 @@
           <t>B057-562; live=https://chillgen.com/products/custom-octopus-welcome-mat-87bf0d33b5</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0005;LIM-0006;LIM-0007;AUTO-0008</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2506,29 +2579,29 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2538,7 +2611,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>LIM-0003;LIM-0004</t>
+          <t>LIM-0005;LIM-0006;LIM-0007;AUTO-0008</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2645,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -2598,21 +2671,21 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2652,7 +2725,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2692,7 +2765,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2718,21 +2791,21 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2742,7 +2815,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>LIM-0005;LIM-0006</t>
+          <t>LIM-0009;LIM-0010;LIM-0011;AUTO-0012</t>
         </is>
       </c>
     </row>
@@ -2762,21 +2835,21 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 30, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2802,21 +2875,21 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 30, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2856,7 +2929,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 124; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -2896,7 +2969,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 70 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2914,29 +2987,29 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2944,7 +3017,11 @@
           <t>B057-563; live=https://chillgen.com/products/custom-octopus-welcome-mat-entryway-464c692e0a</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0009;LIM-0010;LIM-0011;AUTO-0012</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2954,29 +3031,29 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2986,7 +3063,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>LIM-0005;LIM-0006</t>
+          <t>LIM-0009;LIM-0010;LIM-0011;AUTO-0012</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3097,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3046,21 +3123,21 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3100,7 +3177,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3140,7 +3217,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3166,21 +3243,21 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -3190,7 +3267,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>LIM-0007;LIM-0008</t>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016</t>
         </is>
       </c>
     </row>
@@ -3210,21 +3287,21 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 32, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3250,21 +3327,21 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 32, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3290,21 +3367,21 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 117; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -3344,7 +3421,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 67 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -3362,29 +3439,29 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3392,7 +3469,11 @@
           <t>B057-564; live=https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-cf228fd538</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3402,29 +3483,29 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3434,7 +3515,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>LIM-0007;LIM-0008</t>
+          <t>LIM-0013;LIM-0014;LIM-0015;AUTO-0016</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3549,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3494,21 +3575,21 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -3548,7 +3629,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3588,7 +3669,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3614,21 +3695,21 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -3638,7 +3719,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>LIM-0009;LIM-0010</t>
+          <t>LIM-0017;LIM-0018;LIM-0019;AUTO-0020</t>
         </is>
       </c>
     </row>
@@ -3658,21 +3739,21 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 27, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -3698,21 +3779,21 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 27, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -3738,21 +3819,21 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 113; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -3792,7 +3873,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 69 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3810,29 +3891,29 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -3840,7 +3921,11 @@
           <t>B057-565; live=https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0017;LIM-0018;LIM-0019;AUTO-0020</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3850,29 +3935,29 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3882,7 +3967,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>LIM-0009;LIM-0010</t>
+          <t>LIM-0017;LIM-0018;LIM-0019;AUTO-0020</t>
         </is>
       </c>
     </row>
@@ -3916,7 +4001,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3942,21 +4027,21 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3996,7 +4081,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -4036,7 +4121,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -4062,21 +4147,21 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -4086,7 +4171,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>LIM-0011;LIM-0012</t>
+          <t>LIM-0021;LIM-0022;LIM-0023;AUTO-0024</t>
         </is>
       </c>
     </row>
@@ -4106,21 +4191,21 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 33, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4146,21 +4231,21 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 33, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -4186,21 +4271,21 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 119; product specificity is acceptable but borderline.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -4240,7 +4325,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 67 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -4258,29 +4343,29 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -4288,7 +4373,11 @@
           <t>B057-566; live=https://chillgen.com/products/custom-octopus-coastal-welcome-mat-330b515744</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0021;LIM-0022;LIM-0023;AUTO-0024</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4298,29 +4387,29 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -4330,7 +4419,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>LIM-0011;LIM-0012</t>
+          <t>LIM-0021;LIM-0022;LIM-0023;AUTO-0024</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4453,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -4390,21 +4479,21 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -4444,7 +4533,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -4484,7 +4573,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -4510,21 +4599,21 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4534,7 +4623,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>LIM-0013;LIM-0014</t>
+          <t>LIM-0025;LIM-0026;LIM-0027;AUTO-0028</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4657,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 35; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -4608,7 +4697,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 35; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -4648,7 +4737,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 126; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -4688,7 +4777,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 67 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -4706,29 +4795,29 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -4736,7 +4825,11 @@
           <t>B057-567; live=https://chillgen.com/products/custom-octopus-coastal-welcome-mat-2e91144f8b</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0025;LIM-0026;LIM-0027;AUTO-0028</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4746,29 +4839,29 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4778,7 +4871,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>LIM-0013;LIM-0014</t>
+          <t>LIM-0025;LIM-0026;LIM-0027;AUTO-0028</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4905,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4838,21 +4931,21 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4892,7 +4985,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4932,7 +5025,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4958,21 +5051,21 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4982,7 +5075,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>LIM-0015;LIM-0016</t>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032</t>
         </is>
       </c>
     </row>
@@ -5002,21 +5095,21 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 29, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -5042,21 +5135,21 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 29, but keyword coverage or length is borderline.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -5096,7 +5189,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 122; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -5136,7 +5229,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 71 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -5154,29 +5247,29 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -5184,7 +5277,11 @@
           <t>B057-568; live=https://chillgen.com/products/custom-octopus-welcome-mat-coastal-front-door-5012959a0b</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5194,29 +5291,29 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -5226,7 +5323,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>LIM-0015;LIM-0016</t>
+          <t>LIM-0029;LIM-0030;LIM-0031;AUTO-0032</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5357,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>PDP URL/H1, Product_Evidence, and local image contact sheet match the proposed product type and motif; no product/variant mix-up found.</t>
+          <t>Live PDP is reachable and workbook/evidence/image rows align for this product.</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -5286,21 +5383,21 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>10</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Claims in proposed copy are supported by live PDP text and/or feature images: rug form, indoor use, personalization where present, soft printed surface, size/backing graphics, and non-slip/anti-slip backing.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -5340,7 +5437,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Primary keyword is motif-specific and matches the product's visual job-to-be-done; broad Halloween rug is explicitly kept as collection/rejected.</t>
+          <t>Primary keyword is long-tail and has a matching PRIMARY row in Keyword_Map.</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -5380,7 +5477,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map assigns the primary query to PRODUCT and broad head term to COLLECTION, matching product-page intent.</t>
+          <t>PRIMARY keyword maps to product page intent.</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -5406,21 +5503,21 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Demand evidence is honest but limited: category/SERP references only, no paid volume and no direct Chillgen customer query/review data.</t>
+          <t>Direct/volume/customer demand evidence is present.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -5430,7 +5527,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>LIM-0017;LIM-0018</t>
+          <t>LIM-0033;LIM-0034;LIM-0035;AUTO-0036</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5561,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SEO title is readable English, specific to the motif, not stuffed, and better differentiated than the current generic live title.</t>
+          <t>Readable title length 40; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -5504,7 +5601,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Proposed Product Title/H1 is specific and consistent with the product; it does not conflate SEO title with an unrelated H1.</t>
+          <t>Readable title length 40; overlaps primary keyword terms.</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -5544,7 +5641,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Meta description is concrete, readable, and tied to observed motif/material/backing facts without unsupported delivery or ranking claims.</t>
+          <t>Meta length 127; shares product-specific terms.</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -5584,7 +5681,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Proposed HTML is complete enough for the intended SET action and preserves the essential product facts in concise buyer-facing copy.</t>
+          <t>Structured buyer-facing HTML with 69 content words and product-specific overlap.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -5602,29 +5699,29 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>All Image_Audit rows for this product were visually checked through local B057 contact sheets; live gallery count matches workbook/evidence.</t>
+          <t>Evidence is cross-linked, but identity/admin before-state is not fully verified.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -5632,7 +5729,11 @@
           <t>B057-569; live=https://chillgen.com/products/personalized-teacher-round-rug-with-name-0e0fa122bd</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0033;LIM-0034;LIM-0035;AUTO-0036</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5642,29 +5743,29 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Workbook links SEO_Products, Product_Evidence, Image_Audit, Keyword_Map and Buyer_Search_Research, but B057 identity/admin SEO before-state remains non-admin/public JSON only.</t>
+          <t>Image score is derived from per-image evidence rules over Image_Audit observation and alt text; direct visual confirmation is still a limitation.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5674,7 +5775,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>LIM-0017;LIM-0018</t>
+          <t>LIM-0033;LIM-0034;LIM-0035;AUTO-0036</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5801,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="53" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
@@ -5875,17 +5976,17 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Main image shows personalized green 19th Hole golf rug in home office.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -5905,12 +6006,12 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -5924,24 +6025,24 @@
         </is>
       </c>
       <c r="R2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_01.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -5979,17 +6080,17 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side scene shows Anderson's golf rug and club artwork.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -6009,12 +6110,12 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -6028,24 +6129,24 @@
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_02.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -6083,17 +6184,17 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart lists small, medium and large rug sizes.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -6113,12 +6214,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6132,24 +6233,24 @@
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_03.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -6187,17 +6288,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up shows quick dry microfiber surface and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -6217,12 +6318,12 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6236,24 +6337,24 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_04.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -6291,17 +6392,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -6321,12 +6422,12 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -6340,24 +6441,24 @@
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_05.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -6395,17 +6496,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Bright living room mockup shows full golf rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -6425,12 +6526,12 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6444,24 +6545,24 @@
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_06.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -6499,17 +6600,17 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Patio-style placement shows rug scale.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -6529,12 +6630,12 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6548,24 +6649,24 @@
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_07.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -6603,17 +6704,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Cozy fireplace scene with person near golf rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -6633,12 +6734,12 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -6652,24 +6753,24 @@
         </is>
       </c>
       <c r="R9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B057-561; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_08.jpg</t>
+          <t>B057-561; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-golf-area-rug-d8623da216__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -6707,17 +6808,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Main image shows skull over teal octopus tentacles by sofa.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -6737,12 +6838,12 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6756,24 +6857,24 @@
         </is>
       </c>
       <c r="R10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S10" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B057-562; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_01.jpg</t>
+          <t>B057-562; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -6811,17 +6912,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart shows three rectangular rug sizes.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -6841,12 +6942,12 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6860,24 +6961,24 @@
         </is>
       </c>
       <c r="R11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S11" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B057-562; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_02.jpg</t>
+          <t>B057-562; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -6915,17 +7016,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up shows tentacles and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -6945,12 +7046,12 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6964,24 +7065,24 @@
         </is>
       </c>
       <c r="R12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S12" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>B057-562; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_03.jpg</t>
+          <t>B057-562; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -7019,17 +7120,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Living room mockup with octopus skull rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -7049,12 +7150,12 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7068,24 +7169,24 @@
         </is>
       </c>
       <c r="R13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S13" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>B057-562; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_04.jpg</t>
+          <t>B057-562; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -7123,17 +7224,17 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Family scene shows rug scale and soft use.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -7153,12 +7254,12 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7172,24 +7273,24 @@
         </is>
       </c>
       <c r="R14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W14" s="2" t="inlineStr"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>B057-562; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_05.jpg</t>
+          <t>B057-562; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -7227,17 +7328,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -7257,12 +7358,12 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -7276,24 +7377,24 @@
         </is>
       </c>
       <c r="R15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S15" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>B057-562; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_06.jpg</t>
+          <t>B057-562; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -7331,17 +7432,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side image shows full skull octopus design.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -7361,12 +7462,12 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7380,24 +7481,24 @@
         </is>
       </c>
       <c r="R16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S16" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>B057-562; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_07.jpg</t>
+          <t>B057-562; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-87bf0d33b5__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -7435,17 +7536,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Main sofa-side scene shows glowing blue octopus tentacle rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -7465,12 +7566,12 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7484,24 +7585,24 @@
         </is>
       </c>
       <c r="R17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S17" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>B057-563; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_01.jpg</t>
+          <t>B057-563; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -7539,17 +7640,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart lists three rectangular sizes.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -7569,12 +7670,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -7588,24 +7689,24 @@
         </is>
       </c>
       <c r="R18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S18" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>B057-563; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_02.jpg</t>
+          <t>B057-563; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -7643,17 +7744,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up shows blue suction cups and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -7673,12 +7774,12 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -7692,24 +7793,24 @@
         </is>
       </c>
       <c r="R19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S19" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>B057-563; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_03.jpg</t>
+          <t>B057-563; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -7747,17 +7848,17 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Living room mockup displays full tentacle rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -7777,12 +7878,12 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7796,24 +7897,24 @@
         </is>
       </c>
       <c r="R20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S20" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>B057-563; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_04.jpg</t>
+          <t>B057-563; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -7851,17 +7952,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Family scene shows scale and softness.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -7881,12 +7982,12 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7900,24 +8001,24 @@
         </is>
       </c>
       <c r="R21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S21" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>B057-563; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_05.jpg</t>
+          <t>B057-563; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -7955,17 +8056,17 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -7985,12 +8086,12 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8004,24 +8105,24 @@
         </is>
       </c>
       <c r="R22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S22" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>B057-563; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_06.jpg</t>
+          <t>B057-563; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -8059,17 +8160,17 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side room image with full dark octopus design.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -8089,12 +8190,12 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8108,24 +8209,24 @@
         </is>
       </c>
       <c r="R23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S23" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>B057-563; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_07.jpg</t>
+          <t>B057-563; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-entryway-464c692e0a__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -8163,17 +8264,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Main image shows turquoise octopus mandala rug beside sofa.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -8193,12 +8294,12 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8212,24 +8313,24 @@
         </is>
       </c>
       <c r="R24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S24" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>B057-564; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_01.jpg</t>
+          <t>B057-564; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -8267,17 +8368,17 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart shows three rectangular options.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -8297,12 +8398,12 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -8316,24 +8417,24 @@
         </is>
       </c>
       <c r="R25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S25" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>B057-564; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_02.jpg</t>
+          <t>B057-564; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -8371,17 +8472,17 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up highlights ornate octopus lines and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -8401,12 +8502,12 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -8420,24 +8521,24 @@
         </is>
       </c>
       <c r="R26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S26" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B057-564; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_03.jpg</t>
+          <t>B057-564; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -8475,17 +8576,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Living room mockup shows full turquoise design.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -8505,12 +8606,12 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -8524,24 +8625,24 @@
         </is>
       </c>
       <c r="R27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S27" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B057-564; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_04.jpg</t>
+          <t>B057-564; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -8579,17 +8680,17 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Family scene shows rug scale.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -8609,12 +8710,12 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -8628,24 +8729,24 @@
         </is>
       </c>
       <c r="R28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S28" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B057-564; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_05.jpg</t>
+          <t>B057-564; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -8683,17 +8784,17 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -8713,12 +8814,12 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -8732,24 +8833,24 @@
         </is>
       </c>
       <c r="R29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S29" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>B057-564; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_06.jpg</t>
+          <t>B057-564; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -8787,17 +8888,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side image displays full octopus mandala rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -8817,12 +8918,12 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -8836,24 +8937,24 @@
         </is>
       </c>
       <c r="R30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S30" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>B057-564; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_07.jpg</t>
+          <t>B057-564; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-cf228fd538__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -8891,17 +8992,17 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Main image shows red octopus mosaic rug in sofa-side room.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -8921,12 +9022,12 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -8940,24 +9041,24 @@
         </is>
       </c>
       <c r="R31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S31" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B057-565; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_01.jpg</t>
+          <t>B057-565; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -8995,17 +9096,17 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart shows three rug sizes.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -9025,12 +9126,12 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -9044,24 +9145,24 @@
         </is>
       </c>
       <c r="R32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S32" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W32" s="2" t="inlineStr"/>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>B057-565; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_02.jpg</t>
+          <t>B057-565; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -9099,17 +9200,17 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up shows mosaic texture and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -9129,12 +9230,12 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -9148,24 +9249,24 @@
         </is>
       </c>
       <c r="R33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S33" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>B057-565; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_03.jpg</t>
+          <t>B057-565; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -9203,17 +9304,17 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Living room mockup displays full red octopus rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -9233,12 +9334,12 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -9252,24 +9353,24 @@
         </is>
       </c>
       <c r="R34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S34" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>B057-565; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_04.jpg</t>
+          <t>B057-565; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -9307,17 +9408,17 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Family scene shows rug scale.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -9337,12 +9438,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -9356,24 +9457,24 @@
         </is>
       </c>
       <c r="R35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S35" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>B057-565; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_05.jpg</t>
+          <t>B057-565; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -9411,17 +9512,17 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -9441,12 +9542,12 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -9460,24 +9561,24 @@
         </is>
       </c>
       <c r="R36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S36" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>B057-565; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_06.jpg</t>
+          <t>B057-565; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9616,17 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side image shows full stained-glass style design.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -9545,12 +9646,12 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -9564,24 +9665,24 @@
         </is>
       </c>
       <c r="R37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S37" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>B057-565; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_07.jpg</t>
+          <t>B057-565; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -9619,17 +9720,17 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Main image shows cream octopus on teal vintage rug beside sofa.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -9649,12 +9750,12 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9668,24 +9769,24 @@
         </is>
       </c>
       <c r="R38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S38" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W38" s="2" t="inlineStr"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>B057-566; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_01.jpg</t>
+          <t>B057-566; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -9723,17 +9824,17 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart lists three rectangular sizes.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -9753,12 +9854,12 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -9772,24 +9873,24 @@
         </is>
       </c>
       <c r="R39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S39" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>B057-566; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_02.jpg</t>
+          <t>B057-566; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -9827,17 +9928,17 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up shows antique border and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -9857,12 +9958,12 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -9876,24 +9977,24 @@
         </is>
       </c>
       <c r="R40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S40" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W40" s="2" t="inlineStr"/>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>B057-566; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_03.jpg</t>
+          <t>B057-566; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -9931,17 +10032,17 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Living room mockup shows full vintage octopus rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -9961,12 +10062,12 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -9980,24 +10081,24 @@
         </is>
       </c>
       <c r="R41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S41" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>B057-566; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_04.jpg</t>
+          <t>B057-566; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -10035,17 +10136,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Family image shows rug scale.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -10065,12 +10166,12 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -10084,24 +10185,24 @@
         </is>
       </c>
       <c r="R42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S42" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W42" s="2" t="inlineStr"/>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>B057-566; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_05.jpg</t>
+          <t>B057-566; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -10139,17 +10240,17 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -10169,12 +10270,12 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -10188,24 +10289,24 @@
         </is>
       </c>
       <c r="R43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S43" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>B057-566; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_06.jpg</t>
+          <t>B057-566; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -10243,17 +10344,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side view shows cream octopus artwork.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -10273,12 +10374,12 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10292,24 +10393,24 @@
         </is>
       </c>
       <c r="R44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S44" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>B057-566; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_07.jpg</t>
+          <t>B057-566; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-330b515744__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -10347,17 +10448,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Living room image shows colorful watercolor octopus rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -10377,12 +10478,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -10396,24 +10497,24 @@
         </is>
       </c>
       <c r="R45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S45" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>B057-567; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_01.jpg</t>
+          <t>B057-567; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -10451,17 +10552,17 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side mockup shows full rainbow octopus design.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -10481,12 +10582,12 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -10500,24 +10601,24 @@
         </is>
       </c>
       <c r="R46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S46" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>B057-567; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_02.jpg</t>
+          <t>B057-567; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -10555,17 +10656,17 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart displays three rug options.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -10585,12 +10686,12 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -10604,24 +10705,24 @@
         </is>
       </c>
       <c r="R47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S47" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W47" s="2" t="inlineStr"/>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>B057-567; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_03.jpg</t>
+          <t>B057-567; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -10659,17 +10760,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Family scene shows scale and soft use.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -10689,12 +10790,12 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -10708,24 +10809,24 @@
         </is>
       </c>
       <c r="R48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S48" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>B057-567; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_04.jpg</t>
+          <t>B057-567; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -10763,17 +10864,17 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -10793,12 +10894,12 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -10812,24 +10913,24 @@
         </is>
       </c>
       <c r="R49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S49" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V49" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>B057-567; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_05.jpg</t>
+          <t>B057-567; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -10867,17 +10968,17 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side placement image with watercolor octopus rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -10897,12 +10998,12 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -10916,24 +11017,24 @@
         </is>
       </c>
       <c r="R50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S50" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W50" s="2" t="inlineStr"/>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>B057-567; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_06.jpg</t>
+          <t>B057-567; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -10971,17 +11072,17 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up shows quick dry microfiber and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -11001,12 +11102,12 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -11020,24 +11121,24 @@
         </is>
       </c>
       <c r="R51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S51" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V51" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W51" s="2" t="inlineStr"/>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>B057-567; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_07.jpg</t>
+          <t>B057-567; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-coastal-welcome-mat-2e91144f8b__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -11075,17 +11176,17 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Main image shows teal octopus rug by sofa.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -11105,12 +11206,12 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -11124,24 +11225,24 @@
         </is>
       </c>
       <c r="R52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S52" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V52" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W52" s="2" t="inlineStr"/>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>B057-568; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_01.jpg</t>
+          <t>B057-568; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -11179,17 +11280,17 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart lists small, medium and large options.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -11209,12 +11310,12 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -11228,24 +11329,24 @@
         </is>
       </c>
       <c r="R53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S53" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V53" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W53" s="2" t="inlineStr"/>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>B057-568; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_02.jpg</t>
+          <t>B057-568; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -11283,17 +11384,17 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Close-up shows teal tentacles, gold suction cups and memory foam cushion.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -11313,12 +11414,12 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -11332,24 +11433,24 @@
         </is>
       </c>
       <c r="R54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S54" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V54" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W54" s="2" t="inlineStr"/>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>B057-568; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_03.jpg</t>
+          <t>B057-568; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -11387,17 +11488,17 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Living room mockup shows full rug placement.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -11417,12 +11518,12 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -11436,24 +11537,24 @@
         </is>
       </c>
       <c r="R55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S55" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V55" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W55" s="2" t="inlineStr"/>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>B057-568; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_04.jpg</t>
+          <t>B057-568; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -11491,17 +11592,17 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Family scene shows rug scale and softness.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -11521,12 +11622,12 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -11540,24 +11641,24 @@
         </is>
       </c>
       <c r="R56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S56" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V56" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W56" s="2" t="inlineStr"/>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>B057-568; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_05.jpg</t>
+          <t>B057-568; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -11595,17 +11696,17 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing panel shows anti slip and stain resistance.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -11625,12 +11726,12 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -11644,24 +11745,24 @@
         </is>
       </c>
       <c r="R57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S57" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V57" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W57" s="2" t="inlineStr"/>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>B057-568; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_06.jpg</t>
+          <t>B057-568; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -11699,17 +11800,17 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Sofa-side image shows full teal coastal design.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -11729,12 +11830,12 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -11748,24 +11849,24 @@
         </is>
       </c>
       <c r="R58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S58" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V58" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W58" s="2" t="inlineStr"/>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>B057-568; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_07.jpg</t>
+          <t>B057-568; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/custom-octopus-welcome-mat-coastal-front-door-5012959a0b__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -11803,17 +11904,17 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Classroom mockup shows round Mrs Smith welcome rug.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -11833,12 +11934,12 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -11852,24 +11953,24 @@
         </is>
       </c>
       <c r="R59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S59" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V59" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W59" s="2" t="inlineStr"/>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_01.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_01.jpg</t>
         </is>
       </c>
     </row>
@@ -11907,17 +12008,17 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Child reading on round teacher rug for scale.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -11937,12 +12038,12 @@
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -11956,24 +12057,24 @@
         </is>
       </c>
       <c r="R60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S60" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V60" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W60" s="2" t="inlineStr"/>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_02.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_02.jpg</t>
         </is>
       </c>
     </row>
@@ -12011,17 +12112,17 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Size chart shows four round rug options.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -12041,12 +12142,12 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -12060,24 +12161,24 @@
         </is>
       </c>
       <c r="R61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S61" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V61" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W61" s="2" t="inlineStr"/>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_03.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_03.jpg</t>
         </is>
       </c>
     </row>
@@ -12115,17 +12216,17 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Group classroom scene shows storytime use.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -12145,12 +12246,12 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -12164,24 +12265,24 @@
         </is>
       </c>
       <c r="R62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S62" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V62" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_04.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_04.jpg</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12320,17 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing callout shows non slip TPR bottom.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -12249,12 +12350,12 @@
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -12268,24 +12369,24 @@
         </is>
       </c>
       <c r="R63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S63" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V63" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_05.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_05.jpg</t>
         </is>
       </c>
     </row>
@@ -12323,17 +12424,17 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Design callout highlights colorful teacher name and speckle border.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -12353,12 +12454,12 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -12372,24 +12473,24 @@
         </is>
       </c>
       <c r="R64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S64" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V64" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W64" s="2" t="inlineStr"/>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_06.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_06.jpg</t>
         </is>
       </c>
     </row>
@@ -12427,17 +12528,17 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Backing image notes soft comfortable non slip underside.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -12457,12 +12558,12 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -12476,24 +12577,24 @@
         </is>
       </c>
       <c r="R65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S65" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V65" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W65" s="2" t="inlineStr"/>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_07.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_07.jpg</t>
         </is>
       </c>
     </row>
@@ -12531,17 +12632,17 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>LIVE_GALLERY_COUNT_PLUS_LOCAL_CONTACT_SHEET_VISUAL_QA</t>
+          <t>EVIDENCE_RULES_FROM_IMAGE_AUDIT_ALT_AND_OBSERVATION</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T13:58:59.436765+00:00</t>
+          <t>2026-09-07T16:54:34.785003+00:00</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>QA visual check matched workbook observation: Multi-room graphic shows nursery, living room and kids playroom use.</t>
+          <t>Image URL and workbook observation exist; actual visual match still depends on reviewer/contact-sheet confirmation. Observation is present and not internal-language, but not independently re-seen by this script. Alt is present, practical length, and overlaps product/observation terms. Alt is concise and not keyword-stuffed.</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -12561,12 +12662,12 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -12580,24 +12681,24 @@
         </is>
       </c>
       <c r="R66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S66" s="2" t="n">
         <v>100</v>
       </c>
       <c r="T66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="U66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V66" s="2" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="W66" s="2" t="inlineStr"/>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>B057-569; local B057 contact sheet; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_08.jpg</t>
+          <t>B057-569; seo_runs/chillgen.com/chillgen_20260907_01/evidence/images/B057/personalized-teacher-round-rug-with-name-0e0fa122bd__img_08.jpg</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12867,7 +12968,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-87bf0d33b5</t>
+          <t>chillgen.com::custom-golf-area-rug-d8623da216</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -12878,90 +12979,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-octopus-welcome-mat-87bf0d33b5; B057-562</t>
+          <t>https://chillgen.com/products/custom-golf-area-rug-d8623da216; B057-561</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>LIM-0004</t>
+          <t>AUTO-0004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-87bf0d33b5</t>
+          <t>chillgen.com::custom-golf-area-rug-d8623da216</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>octopus skull rug</t>
-        </is>
-      </c>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-golf-area-rug-d8623da216; B057-561</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
@@ -12973,7 +13066,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-entryway-464c692e0a</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-87bf0d33b5</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
@@ -13009,7 +13102,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-octopus-welcome-mat-entryway-464c692e0a; B057-563</t>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-87bf0d33b5; B057-562</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -13026,7 +13119,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-entryway-464c692e0a</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-87bf0d33b5</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
@@ -13042,7 +13135,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>blue octopus tentacle rug</t>
+          <t>octopus skull rug</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13079,7 +13172,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-cf228fd538</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-87bf0d33b5</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
@@ -13090,90 +13183,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-cf228fd538; B057-564</t>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-87bf0d33b5; B057-562</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LIM-0008</t>
+          <t>AUTO-0008</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-cf228fd538</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-87bf0d33b5</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>octopus mandala rug</t>
-        </is>
-      </c>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-87bf0d33b5; B057-562</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
@@ -13185,7 +13270,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-entryway-464c692e0a</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
@@ -13221,7 +13306,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da; B057-565</t>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-entryway-464c692e0a; B057-563</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -13238,7 +13323,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-entryway-464c692e0a</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -13254,7 +13339,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>red octopus mosaic rug</t>
+          <t>blue octopus tentacle rug</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -13291,7 +13376,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-coastal-welcome-mat-330b515744</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-entryway-464c692e0a</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -13302,90 +13387,82 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-330b515744; B057-566</t>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-entryway-464c692e0a; B057-563</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIM-0012</t>
+          <t>AUTO-0012</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-coastal-welcome-mat-330b515744</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-entryway-464c692e0a</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>vintage octopus coastal rug</t>
-        </is>
-      </c>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-entryway-464c692e0a; B057-563</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13474,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-coastal-welcome-mat-2e91144f8b</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-cf228fd538</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -13433,7 +13510,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-2e91144f8b; B057-567</t>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-cf228fd538; B057-564</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -13450,7 +13527,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-coastal-welcome-mat-2e91144f8b</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-cf228fd538</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -13466,7 +13543,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>watercolor octopus rug</t>
+          <t>octopus mandala rug</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -13503,7 +13580,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-coastal-front-door-5012959a0b</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-cf228fd538</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -13514,90 +13591,82 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>admin_identity_and_admin_seo_fields</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
-        </is>
-      </c>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/custom-octopus-welcome-mat-coastal-front-door-5012959a0b; B057-568</t>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-cf228fd538; B057-564</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIM-0016</t>
+          <t>AUTO-0016</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::custom-octopus-welcome-mat-coastal-front-door-5012959a0b</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-cf228fd538</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>LIMITATION</t>
+          <t>MAJOR</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>keyword_demand_evidence</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>teal octopus coastal rug</t>
-        </is>
-      </c>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+          <t>Unsupported protected claims found: outdoor</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-cf228fd538; B057-564</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+          <t>Field passes evidence-driven QA rule.</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13678,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-teacher-round-rug-with-name-0e0fa122bd</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -13645,7 +13714,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://chillgen.com/products/personalized-teacher-round-rug-with-name-0e0fa122bd; B057-569</t>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da; B057-565</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -13662,7 +13731,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>chillgen.com::personalized-teacher-round-rug-with-name-0e0fa122bd</t>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
@@ -13678,47 +13747,979 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>red octopus mosaic rug</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da; B057-565</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-for-front-door-and-entryway-6c5a0747da; B057-565</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-330b515744</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-330b515744; B057-566</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-330b515744</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>vintage octopus coastal rug</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-330b515744</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-330b515744; B057-566</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-330b515744</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-330b515744; B057-566</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-2e91144f8b</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-2e91144f8b; B057-567</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-2e91144f8b</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>watercolor octopus rug</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-2e91144f8b</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-2e91144f8b; B057-567</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-coastal-welcome-mat-2e91144f8b</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-coastal-welcome-mat-2e91144f8b; B057-567</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-welcome-mat-coastal-front-door-5012959a0b</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-coastal-front-door-5012959a0b; B057-568</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-welcome-mat-coastal-front-door-5012959a0b</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>teal octopus coastal rug</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-welcome-mat-coastal-front-door-5012959a0b</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-coastal-front-door-5012959a0b; B057-568</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::custom-octopus-welcome-mat-coastal-front-door-5012959a0b</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/custom-octopus-welcome-mat-coastal-front-door-5012959a0b; B057-568</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-teacher-round-rug-with-name-0e0fa122bd</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>admin_identity_and_admin_seo_fields</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC_JSON_MATCHED_TO_HANDLE</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Live storefront URL/H1/canonical returned HTTP 200 and matched the handle, but B057 source identity remains PUBLIC_JSON_MATCHED_TO_HANDLE and Shopify admin/export SEO values were not provided.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Content QA can proceed from storefront/workbook evidence; deployment still needs admin/export identity and before-state verification.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Before approval/deploy, export current Shopify product/admin SEO/media data and confirm product ID, Handle, SEO title, SEO description, Product Title, Body HTML, and media rows.</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-teacher-round-rug-with-name-0e0fa122bd; B057-569</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Admin/export before-state matches the workbook product and intended fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-teacher-round-rug-with-name-0e0fa122bd</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>keyword_demand_evidence</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>personalized teacher round rug</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Keyword_Map records SERP/category pages and no paid volume or direct Chillgen customer query data; Buyer_Search_Research is SUPPORTED_CATEGORY_LANGUAGE_NO_VOLUME.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>The long-tail choice is product-appropriate, but demand proof is category/SERP-level rather than direct customer or volume evidence.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>If a stricter approval standard is required, add Search Console/internal search/review data or a fresh SERP note for the primary keyword.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Marketplace scan: golf rugs use custom golf area rug, golf decor, home office, man cave, personalized name and non slip rug wording.; Marketplace scan: octopus rugs are searched with coastal, nautical, ocean, sea life, octopus skull, mandala, mosaic, watercolor and beach house terms.; Marketplace scan: teacher round rugs use personalized teacher name, classroom decor, round rug, reading corner, storytime and back-to-school modifiers.</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Direct or stronger query evidence is attached, or reviewer accepts the stated limitation.</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>LIM-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-teacher-round-rug-with-name-0e0fa122bd</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>independent_manual_qa_not_recorded</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>This corrected agent report has workbook/live-check metadata, but no reliable per-product semantic QA decisions or per-image visual QA decisions were recorded.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>The previous generator assigned FULL image/product criteria and fixed 95.0 scores. Corrected reports must not infer QA_PASS without explicit independent assessments.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Run manual QA in the console or capture structured reviewer assessments for P1/P2/K1/K2/T1/T2/D1/D2 and every image IM1-IM4, then regenerate.</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-teacher-round-rug-with-name-0e0fa122bd; B057-569</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>A reviewer-provided assessment file exists for this product and its images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>AUTO-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>chillgen.com::personalized-teacher-round-rug-with-name-0e0fa122bd</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>unsupported_claims</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported protected claims found: outdoor</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Remove unsupported claims or add source evidence.</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>https://chillgen.com/products/personalized-teacher-round-rug-with-name-0e0fa122bd; B057-569</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Field passes evidence-driven QA rule.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K19"/>
+  <autoFilter ref="A1:K37"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
